--- a/data/trans_orig/IP1005-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1005-Habitat-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>150058</t>
+          <t>150039</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288199</t>
+          <t>288526</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191945</t>
+          <t>191466</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>209048</t>
+          <t>208177</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>403030</t>
+          <t>402101</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133808</t>
+          <t>133455</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>282902</t>
+          <t>283001</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>204298</t>
+          <t>203869</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412931</t>
+          <t>413218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>602</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>675833</t>
+          <t>676357</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>717355</t>
+          <t>716681</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>722099</t>
+          <t>722098</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1395427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401905</t>
+          <t>1402375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133257</t>
+          <t>132578</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149155</t>
+          <t>149479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284825</t>
+          <t>285401</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201242</t>
+          <t>201262</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>423900</t>
+          <t>423633</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152583</t>
+          <t>152802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318178</t>
+          <t>318346</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203290</t>
+          <t>203014</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>414006</t>
+          <t>414009</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>437</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>701655</t>
+          <t>702025</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>706486</t>
+          <t>706491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>744066</t>
+          <t>743397</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1448271</t>
+          <t>1447737</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1453945</t>
+          <t>1453967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>145334</t>
+          <t>144941</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>277904</t>
+          <t>278123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>476</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201721</t>
+          <t>201918</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>206770</t>
+          <t>206771</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>218483</t>
+          <t>218752</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>223716</t>
+          <t>223721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>423523</t>
+          <t>423355</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>430212</t>
+          <t>430133</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153621</t>
+          <t>153244</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162833</t>
+          <t>163194</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318459</t>
+          <t>318347</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>484</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>698404</t>
+          <t>698706</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>703767</t>
+          <t>703887</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>736743</t>
+          <t>736654</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>743375</t>
+          <t>743461</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1438180</t>
+          <t>1437660</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1445937</t>
+          <t>1446014</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1005-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1005-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3463</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>602</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3038</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3016</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3277</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152475</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>149614</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,74%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152475</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>150039</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>98,02%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>428</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288526</t>
+          <t>288787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1070,102 +1070,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3391</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3697</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3499</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3965</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4248</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1321</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5204</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1178,102 +1178,102 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>211463</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>208751</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>194521</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>191466</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>191664</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,21%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>211463</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>208177</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>405984</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>403057</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>407305</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>405984</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>402101</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>407305</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1306</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4362</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4378</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3969</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1306</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4473</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>136511</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>133455</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>133439</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,05%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>459</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>283001</t>
+          <t>283505</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3517</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3955</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3534</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3921</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>207124</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>204307</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>207124</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>203869</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>579</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413218</t>
+          <t>413605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2099,67 +2099,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5793</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>1948</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4664</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5742</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6019</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>720719</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>716907</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>722098</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679073</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>676357</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>680388</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>675279</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>680389</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>720719</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>716681</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>722098</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2098</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1395427</t>
+          <t>1395102</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1402375</t>
+          <t>1402348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2674,87 +2674,87 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3813</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3328</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3619</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1340</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152419</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>149896</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>135730</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>132578</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>133063</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,52%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152419</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>149479</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>392</t>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>285401</t>
+          <t>285420</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,107 +3012,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>694</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4136</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3323</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3480</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3743</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>316</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>204704</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>201262</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>202075</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>637</t>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>423633</t>
+          <t>423896</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,107 +3355,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2181</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2211</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2478</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154396</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>152802</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>152658</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>495</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318346</t>
+          <t>318613</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,107 +3698,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3329</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>672</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4068</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3490</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3373</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>206410</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>203753</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>206410</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>203014</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,04%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>555</t>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>414009</t>
+          <t>413892</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4724</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1797</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4903</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,06%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4745</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>746791</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>743418</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>705131</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>702025</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>706491</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>701744</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>706486</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,75%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,94%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>746791</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>743397</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2079</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1447737</t>
+          <t>1447882</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1453967</t>
+          <t>1453949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,107 +4616,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3989</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>677</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3135</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3366</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3660</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>147399</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>144087</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>147399</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>144941</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>381</t>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>278123</t>
+          <t>278417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4964,67 +4964,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5609</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1840</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5329</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5607</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>222261</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>218750</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>205407</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>201918</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>206771</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>201891</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>206770</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,11%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,77%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>222261</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>218752</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>223721</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>660</t>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>423355</t>
+          <t>423813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>430133</t>
+          <t>430264</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1097</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3876</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>479</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2753</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2423</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1097</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3479</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>477</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165576</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>162797</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155518</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>153244</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>153574</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,69%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165576</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>163194</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>504</t>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318347</t>
+          <t>318034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>322192</t>
+          <t>322193</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5758,47 +5758,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8470</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2319</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5665</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5496</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3872</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1383</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8190</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>740972</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>736374</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>743485</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1057</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>702052</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>698706</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>703887</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>698875</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>703766</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,93%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>740972</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>736654</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>743461</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1437660</t>
+          <t>1438318</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1446014</t>
+          <t>1446161</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
